--- a/data/trans_orig/Q23-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q23-Clase-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,37; 17,01</t>
+          <t>16,39; 17,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,79</t>
+          <t>16,83; 17,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,68; 17,69</t>
+          <t>16,67; 17,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,32; 19,11</t>
+          <t>17,29; 19,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,33; 19,18</t>
+          <t>17,33; 19,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,74; 17,75</t>
+          <t>16,71; 17,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,79; 17,47</t>
+          <t>16,8; 17,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,17; 18,0</t>
+          <t>17,15; 18,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,55</t>
+          <t>16,82; 17,57</t>
         </is>
       </c>
     </row>
@@ -787,37 +787,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,34; 17,26</t>
+          <t>16,32; 17,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,48; 17,22</t>
+          <t>16,43; 17,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,14; 17,38</t>
+          <t>16,14; 17,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,66; 17,43</t>
+          <t>16,66; 17,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,81; 17,75</t>
+          <t>16,81; 17,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,96; 18,17</t>
+          <t>16,93; 18,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,56; 17,19</t>
+          <t>16,58; 17,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 17,54</t>
+          <t>16,63; 17,49</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,17; 17,13</t>
+          <t>16,19; 17,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,16; 16,87</t>
+          <t>16,18; 16,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,04; 16,93</t>
+          <t>15,98; 16,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,2; 20,08</t>
+          <t>17,13; 19,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,43; 19,37</t>
+          <t>17,45; 19,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,91; 21,55</t>
+          <t>17,89; 21,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 17,33</t>
+          <t>16,47; 17,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,54; 17,22</t>
+          <t>16,54; 17,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 17,43</t>
+          <t>16,5; 17,51</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 16,45</t>
+          <t>16,03; 16,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,99; 16,44</t>
+          <t>15,92; 16,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,15; 16,72</t>
+          <t>16,19; 16,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,74; 17,6</t>
+          <t>16,78; 17,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 18,18</t>
+          <t>16,98; 18,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,17; 18,05</t>
+          <t>17,18; 18,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,69</t>
+          <t>16,31; 16,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,35; 16,82</t>
+          <t>16,37; 16,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,62; 17,12</t>
+          <t>16,66; 17,12</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1117,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,61; 16,39</t>
+          <t>15,58; 16,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 16,83</t>
+          <t>16,0; 16,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,93; 16,81</t>
+          <t>15,95; 16,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,09; 18,87</t>
+          <t>17,05; 18,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,99; 18,12</t>
+          <t>17,0; 18,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,89</t>
+          <t>16,83; 18,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,37; 17,32</t>
+          <t>16,39; 17,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,57; 17,25</t>
+          <t>16,56; 17,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,47; 17,22</t>
+          <t>16,45; 17,17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,2; 16,63</t>
+          <t>15,15; 16,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,42; 16,63</t>
+          <t>15,37; 16,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,37; 16,32</t>
+          <t>15,36; 16,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,05; 18,3</t>
+          <t>17,11; 18,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,36; 19,23</t>
+          <t>17,42; 19,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,49; 19,2</t>
+          <t>17,47; 19,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,64; 17,67</t>
+          <t>16,67; 17,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,01; 18,45</t>
+          <t>16,97; 18,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,01; 18,18</t>
+          <t>16,97; 18,19</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,21; 16,5</t>
+          <t>16,21; 16,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,6</t>
+          <t>16,32; 16,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,69</t>
+          <t>16,31; 16,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,24; 17,77</t>
+          <t>17,19; 17,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,4; 17,96</t>
+          <t>17,39; 17,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,42; 17,93</t>
+          <t>17,39; 17,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,62; 16,91</t>
+          <t>16,61; 16,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,77; 17,06</t>
+          <t>16,79; 17,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,11</t>
+          <t>16,82; 17,13</t>
         </is>
       </c>
     </row>
